--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/124.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/124.xlsx
@@ -426,13 +426,13 @@
         <v>-17.20137628643669</v>
       </c>
       <c r="E2">
-        <v>-12.86867081920663</v>
+        <v>-16.02644367186529</v>
       </c>
       <c r="F2">
-        <v>-0.9970190114199787</v>
+        <v>-0.6331586297402959</v>
       </c>
       <c r="G2">
-        <v>-10.11757666631195</v>
+        <v>-12.13777556213867</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.19009871326401</v>
       </c>
       <c r="E3">
-        <v>-12.68092934379663</v>
+        <v>-14.54168384202239</v>
       </c>
       <c r="F3">
-        <v>-0.7579074471322902</v>
+        <v>-1.029000620107262</v>
       </c>
       <c r="G3">
-        <v>-9.996725995056041</v>
+        <v>-10.56978149674838</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.15629012560952</v>
       </c>
       <c r="E4">
-        <v>-13.45048463123811</v>
+        <v>-15.77610057177326</v>
       </c>
       <c r="F4">
-        <v>-0.9350008007071853</v>
+        <v>-1.109045762239778</v>
       </c>
       <c r="G4">
-        <v>-10.01451677835135</v>
+        <v>-9.939750863897842</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.09676620541292</v>
       </c>
       <c r="E5">
-        <v>-14.34533373752381</v>
+        <v>-16.39854385260156</v>
       </c>
       <c r="F5">
-        <v>-0.9279116324740272</v>
+        <v>-0.639760717940608</v>
       </c>
       <c r="G5">
-        <v>-8.958452338222509</v>
+        <v>-10.79446970547448</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.01166888639012</v>
       </c>
       <c r="E6">
-        <v>-15.57943800256815</v>
+        <v>-16.36319005602367</v>
       </c>
       <c r="F6">
-        <v>-0.6479797793111847</v>
+        <v>-0.7085326080884257</v>
       </c>
       <c r="G6">
-        <v>-8.767298213833937</v>
+        <v>-9.675402530182739</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.89609467582871</v>
       </c>
       <c r="E7">
-        <v>-16.05120083926522</v>
+        <v>-18.65217517031077</v>
       </c>
       <c r="F7">
-        <v>-0.6389704554383372</v>
+        <v>-0.3615468987711716</v>
       </c>
       <c r="G7">
-        <v>-8.333350100154256</v>
+        <v>-8.357618014807908</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.74803523355279</v>
       </c>
       <c r="E8">
-        <v>-16.48609284059184</v>
+        <v>-18.1996628766203</v>
       </c>
       <c r="F8">
-        <v>-0.5159545826529994</v>
+        <v>-0.1280541505766721</v>
       </c>
       <c r="G8">
-        <v>-7.448745892614197</v>
+        <v>-8.454151553086772</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.56434176580547</v>
       </c>
       <c r="E9">
-        <v>-16.67443660304486</v>
+        <v>-19.0190585489902</v>
       </c>
       <c r="F9">
-        <v>-0.6334999171102492</v>
+        <v>-0.3761535011847353</v>
       </c>
       <c r="G9">
-        <v>-7.565439256154289</v>
+        <v>-7.015053714216152</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.34886623777814</v>
       </c>
       <c r="E10">
-        <v>-17.68188621553129</v>
+        <v>-19.79827307149004</v>
       </c>
       <c r="F10">
-        <v>-0.3048020749445998</v>
+        <v>-0.3349397377932515</v>
       </c>
       <c r="G10">
-        <v>-7.058155840621017</v>
+        <v>-6.770350053977443</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.10129406655675</v>
       </c>
       <c r="E11">
-        <v>-18.84930417233867</v>
+        <v>-21.1341774322268</v>
       </c>
       <c r="F11">
-        <v>-0.009610865854787617</v>
+        <v>0.3504340555676007</v>
       </c>
       <c r="G11">
-        <v>-6.533337577074072</v>
+        <v>-6.768017105448678</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.82379407107141</v>
       </c>
       <c r="E12">
-        <v>-19.40695404706522</v>
+        <v>-22.25504267623533</v>
       </c>
       <c r="F12">
-        <v>-0.280102644095327</v>
+        <v>0.7205875444063514</v>
       </c>
       <c r="G12">
-        <v>-5.850397246577487</v>
+        <v>-6.188543534386063</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.51418871355674</v>
       </c>
       <c r="E13">
-        <v>-19.27078283365457</v>
+        <v>-20.65002016217073</v>
       </c>
       <c r="F13">
-        <v>-0.1558003167334416</v>
+        <v>1.185250298597901</v>
       </c>
       <c r="G13">
-        <v>-5.202661142192184</v>
+        <v>-5.139848717879734</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.18425117540636</v>
       </c>
       <c r="E14">
-        <v>-20.33665881778796</v>
+        <v>-23.0752489454526</v>
       </c>
       <c r="F14">
-        <v>-0.2864139753372564</v>
+        <v>1.092135175584014</v>
       </c>
       <c r="G14">
-        <v>-4.321781121122097</v>
+        <v>-5.656496739743662</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.84191520860482</v>
       </c>
       <c r="E15">
-        <v>-21.4330929445251</v>
+        <v>-23.92695980834123</v>
       </c>
       <c r="F15">
-        <v>-0.1180101958177281</v>
+        <v>0.5324296874322633</v>
       </c>
       <c r="G15">
-        <v>-4.598112475972293</v>
+        <v>-4.85612148963455</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.4949052611518</v>
       </c>
       <c r="E16">
-        <v>-22.30132368059372</v>
+        <v>-24.66807175054053</v>
       </c>
       <c r="F16">
-        <v>0.1603750954040877</v>
+        <v>1.088553314934309</v>
       </c>
       <c r="G16">
-        <v>-4.130052782960623</v>
+        <v>-5.025038775514764</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.14762183414637</v>
       </c>
       <c r="E17">
-        <v>-23.28213680896703</v>
+        <v>-25.6685837408472</v>
       </c>
       <c r="F17">
-        <v>0.328787158597644</v>
+        <v>1.581922313102472</v>
       </c>
       <c r="G17">
-        <v>-3.536456834306158</v>
+        <v>-4.279020241759413</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.79756407500399</v>
       </c>
       <c r="E18">
-        <v>-23.81841681485138</v>
+        <v>-26.56595067868117</v>
       </c>
       <c r="F18">
-        <v>0.2951662108202205</v>
+        <v>1.330734808816772</v>
       </c>
       <c r="G18">
-        <v>-3.015927127337408</v>
+        <v>-3.419343474406457</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.4488997875326</v>
       </c>
       <c r="E19">
-        <v>-24.42785431832965</v>
+        <v>-25.45070527091616</v>
       </c>
       <c r="F19">
-        <v>0.2770365618425505</v>
+        <v>1.32246107519761</v>
       </c>
       <c r="G19">
-        <v>-2.900142662169282</v>
+        <v>-2.968467538701599</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.10175317767742</v>
       </c>
       <c r="E20">
-        <v>-25.12272601243663</v>
+        <v>-26.59985989205061</v>
       </c>
       <c r="F20">
-        <v>0.4294395966096036</v>
+        <v>1.755862900342312</v>
       </c>
       <c r="G20">
-        <v>-2.114716657485</v>
+        <v>-1.779943465439534</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.75881404592559</v>
       </c>
       <c r="E21">
-        <v>-25.21670543351781</v>
+        <v>-28.49562855130367</v>
       </c>
       <c r="F21">
-        <v>0.6460030001930895</v>
+        <v>2.016132624832305</v>
       </c>
       <c r="G21">
-        <v>-2.030015204149494</v>
+        <v>-1.757903500224744</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.42144199301719</v>
       </c>
       <c r="E22">
-        <v>-25.89207751854776</v>
+        <v>-29.05921072698027</v>
       </c>
       <c r="F22">
-        <v>0.8562857221285496</v>
+        <v>1.125357678640691</v>
       </c>
       <c r="G22">
-        <v>-1.773892892883918</v>
+        <v>-1.835501108884052</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.09030535439371</v>
       </c>
       <c r="E23">
-        <v>-26.39665367790441</v>
+        <v>-29.81900715293522</v>
       </c>
       <c r="F23">
-        <v>1.040667052113275</v>
+        <v>1.466742795947617</v>
       </c>
       <c r="G23">
-        <v>-1.376290870418205</v>
+        <v>-0.1881605437432732</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.77086166551982</v>
       </c>
       <c r="E24">
-        <v>-26.6323290506856</v>
+        <v>-30.86240379209453</v>
       </c>
       <c r="F24">
-        <v>0.9717717352224399</v>
+        <v>1.785675843169066</v>
       </c>
       <c r="G24">
-        <v>-0.745636805471371</v>
+        <v>0.04267667418522197</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.46970973876264</v>
       </c>
       <c r="E25">
-        <v>-27.11736937317317</v>
+        <v>-30.50408828623761</v>
       </c>
       <c r="F25">
-        <v>1.339159305303243</v>
+        <v>1.280789224632379</v>
       </c>
       <c r="G25">
-        <v>-1.241088136061285</v>
+        <v>-0.2828500355057288</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.1971816937927</v>
       </c>
       <c r="E26">
-        <v>-27.46204511531898</v>
+        <v>-28.83415915422108</v>
       </c>
       <c r="F26">
-        <v>0.8590673798671503</v>
+        <v>1.654646344129046</v>
       </c>
       <c r="G26">
-        <v>-0.3762729757462388</v>
+        <v>-0.6927960134780733</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.95941214805248</v>
       </c>
       <c r="E27">
-        <v>-28.31801274377483</v>
+        <v>-29.53987427933942</v>
       </c>
       <c r="F27">
-        <v>1.041061354997007</v>
+        <v>1.297961280892412</v>
       </c>
       <c r="G27">
-        <v>-0.3678205490091092</v>
+        <v>1.636382391715318</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.76058830126568</v>
       </c>
       <c r="E28">
-        <v>-27.42780079487298</v>
+        <v>-29.53134037007197</v>
       </c>
       <c r="F28">
-        <v>0.9878089281406383</v>
+        <v>1.686379442595489</v>
       </c>
       <c r="G28">
-        <v>-0.1887478824024138</v>
+        <v>1.639168148819286</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.59924109631384</v>
       </c>
       <c r="E29">
-        <v>-28.36531265478494</v>
+        <v>-32.02038667330693</v>
       </c>
       <c r="F29">
-        <v>1.055287736772686</v>
+        <v>1.311947436121279</v>
       </c>
       <c r="G29">
-        <v>-0.2881557707673509</v>
+        <v>0.1175049318483587</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.47920948327067</v>
       </c>
       <c r="E30">
-        <v>-28.50103554926883</v>
+        <v>-31.67333574654409</v>
       </c>
       <c r="F30">
-        <v>1.16472666782614</v>
+        <v>1.671498650571599</v>
       </c>
       <c r="G30">
-        <v>-0.4050788198166039</v>
+        <v>0.7907164404211905</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.40045068497395</v>
       </c>
       <c r="E31">
-        <v>-27.4662475391981</v>
+        <v>-29.78737576199164</v>
       </c>
       <c r="F31">
-        <v>0.913217756988154</v>
+        <v>1.353307820543059</v>
       </c>
       <c r="G31">
-        <v>-0.5970368434872387</v>
+        <v>0.2320064393867415</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.36109221191839</v>
       </c>
       <c r="E32">
-        <v>-27.4338327222512</v>
+        <v>-29.90272731615202</v>
       </c>
       <c r="F32">
-        <v>1.076467434527464</v>
+        <v>1.738409199165326</v>
       </c>
       <c r="G32">
-        <v>-0.3670757117151152</v>
+        <v>0.106712994139345</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.35726107452773</v>
       </c>
       <c r="E33">
-        <v>-27.02124345541235</v>
+        <v>-30.32851029201222</v>
       </c>
       <c r="F33">
-        <v>0.9915548055360976</v>
+        <v>1.254727129405501</v>
       </c>
       <c r="G33">
-        <v>-1.008292028861802</v>
+        <v>-0.7440486942365997</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.38070612324133</v>
       </c>
       <c r="E34">
-        <v>-26.72582392504797</v>
+        <v>-29.91701465164622</v>
       </c>
       <c r="F34">
-        <v>1.169879113071553</v>
+        <v>1.725680505653909</v>
       </c>
       <c r="G34">
-        <v>-0.9982219598958657</v>
+        <v>-0.2191615250369069</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.42788794796523</v>
       </c>
       <c r="E35">
-        <v>-25.99814796522942</v>
+        <v>-29.09988095204316</v>
       </c>
       <c r="F35">
-        <v>1.150054624387755</v>
+        <v>1.24680296683032</v>
       </c>
       <c r="G35">
-        <v>-0.9117748966907353</v>
+        <v>0.5588029818211974</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.49219433210574</v>
       </c>
       <c r="E36">
-        <v>-25.96046200453759</v>
+        <v>-26.22870616238194</v>
       </c>
       <c r="F36">
-        <v>1.026278310326647</v>
+        <v>1.587276879994168</v>
       </c>
       <c r="G36">
-        <v>-1.130068004597473</v>
+        <v>-1.607580896921903</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.56992781702895</v>
       </c>
       <c r="E37">
-        <v>-25.07551214243266</v>
+        <v>-27.55371501465625</v>
       </c>
       <c r="F37">
-        <v>0.9263722313446102</v>
+        <v>1.749091825191829</v>
       </c>
       <c r="G37">
-        <v>-1.390754495052237</v>
+        <v>-0.9530657887947875</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.65522402847521</v>
       </c>
       <c r="E38">
-        <v>-24.32195142518627</v>
+        <v>-26.37954510310344</v>
       </c>
       <c r="F38">
-        <v>1.187334470983344</v>
+        <v>1.944992432279884</v>
       </c>
       <c r="G38">
-        <v>-1.814993474137523</v>
+        <v>-1.07265318975031</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.74119332733631</v>
       </c>
       <c r="E39">
-        <v>-24.39581083625137</v>
+        <v>-24.56706866627345</v>
       </c>
       <c r="F39">
-        <v>0.9679612451695622</v>
+        <v>1.56872476364107</v>
       </c>
       <c r="G39">
-        <v>-1.773312116667896</v>
+        <v>-2.487092648601703</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.82424327424673</v>
       </c>
       <c r="E40">
-        <v>-23.59394035829116</v>
+        <v>-24.89332710463007</v>
       </c>
       <c r="F40">
-        <v>1.181747961218864</v>
+        <v>1.889758550596018</v>
       </c>
       <c r="G40">
-        <v>-1.652674724813352</v>
+        <v>-1.473684088745643</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.90039136914817</v>
       </c>
       <c r="E41">
-        <v>-23.21417347105991</v>
+        <v>-24.97366223352614</v>
       </c>
       <c r="F41">
-        <v>1.096606702824325</v>
+        <v>1.469622201039748</v>
       </c>
       <c r="G41">
-        <v>-2.002167476774487</v>
+        <v>-1.357417284008279</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.97452876703898</v>
       </c>
       <c r="E42">
-        <v>-22.29588498331051</v>
+        <v>-23.66400037966383</v>
       </c>
       <c r="F42">
-        <v>1.215336602667578</v>
+        <v>2.11170302882809</v>
       </c>
       <c r="G42">
-        <v>-1.904577385153482</v>
+        <v>-2.339480334306963</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.05018590617753</v>
       </c>
       <c r="E43">
-        <v>-22.04158399693577</v>
+        <v>-22.93935849743043</v>
       </c>
       <c r="F43">
-        <v>1.119115101893194</v>
+        <v>2.002779342299177</v>
       </c>
       <c r="G43">
-        <v>-1.894700908259554</v>
+        <v>-2.820983192047678</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.13228151679984</v>
       </c>
       <c r="E44">
-        <v>-21.22096110810979</v>
+        <v>-22.97381565615479</v>
       </c>
       <c r="F44">
-        <v>1.522708954415557</v>
+        <v>1.727426704139011</v>
       </c>
       <c r="G44">
-        <v>-2.126742334500365</v>
+        <v>-3.20849217699654</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.22434492643409</v>
       </c>
       <c r="E45">
-        <v>-20.4869950978946</v>
+        <v>-20.96973042711226</v>
       </c>
       <c r="F45">
-        <v>1.359103078893044</v>
+        <v>2.44343103895318</v>
       </c>
       <c r="G45">
-        <v>-2.475441030844114</v>
+        <v>-3.9812821974554</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.33096133628914</v>
       </c>
       <c r="E46">
-        <v>-19.48170556750983</v>
+        <v>-22.07753555208267</v>
       </c>
       <c r="F46">
-        <v>1.374132977049438</v>
+        <v>1.679417842942362</v>
       </c>
       <c r="G46">
-        <v>-2.178040952360724</v>
+        <v>-2.138105204760722</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.45924786844337</v>
       </c>
       <c r="E47">
-        <v>-19.55402982588634</v>
+        <v>-22.0675230960517</v>
       </c>
       <c r="F47">
-        <v>1.350544386887319</v>
+        <v>2.036533657228452</v>
       </c>
       <c r="G47">
-        <v>-2.996476045933019</v>
+        <v>-3.801494224548745</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.61290793949873</v>
       </c>
       <c r="E48">
-        <v>-18.88778714445585</v>
+        <v>-19.80516993740372</v>
       </c>
       <c r="F48">
-        <v>1.734000627847627</v>
+        <v>2.393014942083997</v>
       </c>
       <c r="G48">
-        <v>-3.216029142918584</v>
+        <v>-4.028607256007271</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.79252227200596</v>
       </c>
       <c r="E49">
-        <v>-17.28760556910545</v>
+        <v>-21.8680302305918</v>
       </c>
       <c r="F49">
-        <v>1.476529128444291</v>
+        <v>2.273269463804911</v>
       </c>
       <c r="G49">
-        <v>-3.174620126838392</v>
+        <v>-5.596981943098453</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.99304831756641</v>
       </c>
       <c r="E50">
-        <v>-17.50307036239041</v>
+        <v>-18.40439971498109</v>
       </c>
       <c r="F50">
-        <v>1.689431148107403</v>
+        <v>2.261919173651752</v>
       </c>
       <c r="G50">
-        <v>-3.481007471173101</v>
+        <v>-4.390063341774141</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.211140125208</v>
       </c>
       <c r="E51">
-        <v>-17.19277932338483</v>
+        <v>-17.19915088631363</v>
       </c>
       <c r="F51">
-        <v>1.713399130540004</v>
+        <v>2.279015020110728</v>
       </c>
       <c r="G51">
-        <v>-3.587561860094509</v>
+        <v>-5.221692227236963</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.44055830980496</v>
       </c>
       <c r="E52">
-        <v>-16.06614480349053</v>
+        <v>-17.92809481885432</v>
       </c>
       <c r="F52">
-        <v>1.351470501643649</v>
+        <v>2.44550527092979</v>
       </c>
       <c r="G52">
-        <v>-3.322576969396873</v>
+        <v>-4.825323944077602</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.677736304245</v>
       </c>
       <c r="E53">
-        <v>-15.3523486165055</v>
+        <v>-15.91004377597213</v>
       </c>
       <c r="F53">
-        <v>1.810280011767017</v>
+        <v>1.953882471246728</v>
       </c>
       <c r="G53">
-        <v>-3.756748206142598</v>
+        <v>-5.923204271760007</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.91572196892236</v>
       </c>
       <c r="E54">
-        <v>-15.45447929080049</v>
+        <v>-15.4749706356852</v>
       </c>
       <c r="F54">
-        <v>1.59905129425756</v>
+        <v>2.373766997112547</v>
       </c>
       <c r="G54">
-        <v>-4.456344017274924</v>
+        <v>-4.416588736860692</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.14508104863076</v>
       </c>
       <c r="E55">
-        <v>-14.36798969298419</v>
+        <v>-15.28182669078405</v>
       </c>
       <c r="F55">
-        <v>1.520865008576926</v>
+        <v>1.666463833497384</v>
       </c>
       <c r="G55">
-        <v>-4.631370937698825</v>
+        <v>-5.362801160400884</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.35903465507501</v>
       </c>
       <c r="E56">
-        <v>-14.43252044759349</v>
+        <v>-15.57317059454153</v>
       </c>
       <c r="F56">
-        <v>1.568139936254694</v>
+        <v>2.118222280288122</v>
       </c>
       <c r="G56">
-        <v>-4.216207817446963</v>
+        <v>-5.613374926009439</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.54865591970013</v>
       </c>
       <c r="E57">
-        <v>-13.81259499831346</v>
+        <v>-13.56351081399556</v>
       </c>
       <c r="F57">
-        <v>1.45241038314438</v>
+        <v>1.215863444335759</v>
       </c>
       <c r="G57">
-        <v>-4.772007374958185</v>
+        <v>-5.755514162743025</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.71326712715497</v>
       </c>
       <c r="E58">
-        <v>-13.20332504837347</v>
+        <v>-12.36443429540055</v>
       </c>
       <c r="F58">
-        <v>1.338325967696027</v>
+        <v>2.26364052111477</v>
       </c>
       <c r="G58">
-        <v>-4.970892057340807</v>
+        <v>-4.912266471738208</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-13.84887411103484</v>
       </c>
       <c r="E59">
-        <v>-12.98364877426138</v>
+        <v>-12.3604447097998</v>
       </c>
       <c r="F59">
-        <v>1.59724048311504</v>
+        <v>1.852486987674457</v>
       </c>
       <c r="G59">
-        <v>-5.500687933993429</v>
+        <v>-6.023776993778546</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.9514054673139</v>
       </c>
       <c r="E60">
-        <v>-13.00029091623957</v>
+        <v>-12.52638611133687</v>
       </c>
       <c r="F60">
-        <v>1.459895510996077</v>
+        <v>1.822881136698403</v>
       </c>
       <c r="G60">
-        <v>-5.156340137437503</v>
+        <v>-5.87886512482723</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-14.01603713687845</v>
       </c>
       <c r="E61">
-        <v>-12.49612231954361</v>
+        <v>-13.45207865408881</v>
       </c>
       <c r="F61">
-        <v>1.44649252641878</v>
+        <v>2.164143655629716</v>
       </c>
       <c r="G61">
-        <v>-5.977029430221138</v>
+        <v>-6.221254032112167</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.04072322857764</v>
       </c>
       <c r="E62">
-        <v>-11.96994986764437</v>
+        <v>-11.94908718789104</v>
       </c>
       <c r="F62">
-        <v>1.409437995756753</v>
+        <v>1.709467698846317</v>
       </c>
       <c r="G62">
-        <v>-5.910515787989634</v>
+        <v>-6.450211110087101</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.02901623354558</v>
       </c>
       <c r="E63">
-        <v>-12.34998846331609</v>
+        <v>-12.16684338902387</v>
       </c>
       <c r="F63">
-        <v>1.477145433791973</v>
+        <v>0.6890342016663155</v>
       </c>
       <c r="G63">
-        <v>-5.759303973644183</v>
+        <v>-7.114468165024207</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.98272085673266</v>
       </c>
       <c r="E64">
-        <v>-11.59652737249787</v>
+        <v>-13.04094302740643</v>
       </c>
       <c r="F64">
-        <v>1.30774595665428</v>
+        <v>1.681786973714369</v>
       </c>
       <c r="G64">
-        <v>-5.534881543864403</v>
+        <v>-6.381840296452951</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.90364038038839</v>
       </c>
       <c r="E65">
-        <v>-11.60216985111143</v>
+        <v>-12.56558005387326</v>
       </c>
       <c r="F65">
-        <v>1.004001854130563</v>
+        <v>1.31638914213509</v>
       </c>
       <c r="G65">
-        <v>-6.013749580692883</v>
+        <v>-7.724716313092855</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.78960030971735</v>
       </c>
       <c r="E66">
-        <v>-12.26444558931119</v>
+        <v>-11.87970643761952</v>
       </c>
       <c r="F66">
-        <v>1.370156813516</v>
+        <v>1.269760341031506</v>
       </c>
       <c r="G66">
-        <v>-6.261074936957588</v>
+        <v>-8.289227513844402</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.64595777422918</v>
       </c>
       <c r="E67">
-        <v>-10.97787442441399</v>
+        <v>-12.49187913939842</v>
       </c>
       <c r="F67">
-        <v>1.056447451136605</v>
+        <v>0.9664933781318015</v>
       </c>
       <c r="G67">
-        <v>-6.431019245185908</v>
+        <v>-7.515627031660359</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.47629210178774</v>
       </c>
       <c r="E68">
-        <v>-11.74589003069286</v>
+        <v>-11.48153130354709</v>
       </c>
       <c r="F68">
-        <v>0.9999494807960678</v>
+        <v>1.091790574744449</v>
       </c>
       <c r="G68">
-        <v>-6.239005440748763</v>
+        <v>-7.12556197511669</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.28657144761866</v>
       </c>
       <c r="E69">
-        <v>-11.00746800205412</v>
+        <v>-10.78019294855716</v>
       </c>
       <c r="F69">
-        <v>1.196685082226145</v>
+        <v>1.546726638892326</v>
       </c>
       <c r="G69">
-        <v>-6.483269417298506</v>
+        <v>-7.62251610518083</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.08074402583794</v>
       </c>
       <c r="E70">
-        <v>-11.35812585836406</v>
+        <v>-11.36977309351179</v>
       </c>
       <c r="F70">
-        <v>1.103733975958012</v>
+        <v>0.4987201043427402</v>
       </c>
       <c r="G70">
-        <v>-6.524245312132852</v>
+        <v>-6.691902608934239</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.85950801732139</v>
       </c>
       <c r="E71">
-        <v>-11.6456658439551</v>
+        <v>-10.83449388038313</v>
       </c>
       <c r="F71">
-        <v>1.080246446619035</v>
+        <v>1.524523079027688</v>
       </c>
       <c r="G71">
-        <v>-6.083751161442077</v>
+        <v>-7.142384798051963</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.62819053260353</v>
       </c>
       <c r="E72">
-        <v>-11.38851191895553</v>
+        <v>-10.91757779300186</v>
       </c>
       <c r="F72">
-        <v>0.9602093830141644</v>
+        <v>1.106682963911979</v>
       </c>
       <c r="G72">
-        <v>-5.795915843804467</v>
+        <v>-6.767039301423964</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.39023077859166</v>
       </c>
       <c r="E73">
-        <v>-10.96985449694641</v>
+        <v>-13.32234240224306</v>
       </c>
       <c r="F73">
-        <v>1.23110540454727</v>
+        <v>0.6896306261963311</v>
       </c>
       <c r="G73">
-        <v>-6.051267068003575</v>
+        <v>-6.433591722888513</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.1524516081307</v>
       </c>
       <c r="E74">
-        <v>-11.80098344547018</v>
+        <v>-14.33354159120784</v>
       </c>
       <c r="F74">
-        <v>0.8865840882533443</v>
+        <v>0.9648001951604792</v>
       </c>
       <c r="G74">
-        <v>-6.080168067499163</v>
+        <v>-7.095922700770226</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.91804767902743</v>
       </c>
       <c r="E75">
-        <v>-12.1510978848992</v>
+        <v>-11.9923431716123</v>
       </c>
       <c r="F75">
-        <v>0.5089048815601601</v>
+        <v>1.151476102850959</v>
       </c>
       <c r="G75">
-        <v>-5.831274287329044</v>
+        <v>-5.690322852799977</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.68836003275682</v>
       </c>
       <c r="E76">
-        <v>-13.15585758382507</v>
+        <v>-13.4059606747947</v>
       </c>
       <c r="F76">
-        <v>0.5981697528858348</v>
+        <v>0.9609996455164351</v>
       </c>
       <c r="G76">
-        <v>-5.44159313370783</v>
+        <v>-4.816448239759303</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.46368286269068</v>
       </c>
       <c r="E77">
-        <v>-13.39404625968052</v>
+        <v>-14.35633792936245</v>
       </c>
       <c r="F77">
-        <v>0.8345112565785618</v>
+        <v>0.5415442139652662</v>
       </c>
       <c r="G77">
-        <v>-4.93571079978044</v>
+        <v>-6.949567094332754</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.24661922454954</v>
       </c>
       <c r="E78">
-        <v>-13.85955074529899</v>
+        <v>-14.18563710164332</v>
       </c>
       <c r="F78">
-        <v>0.5662527568559699</v>
+        <v>1.179473264330777</v>
       </c>
       <c r="G78">
-        <v>-5.055173514316704</v>
+        <v>-6.248498014720236</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.04111469822378</v>
       </c>
       <c r="E79">
-        <v>-14.4886146551265</v>
+        <v>-14.96606978365122</v>
       </c>
       <c r="F79">
-        <v>0.5933652219495977</v>
+        <v>0.5282050136779858</v>
       </c>
       <c r="G79">
-        <v>-5.011657953995348</v>
+        <v>-5.073892883313336</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.84748519319806</v>
       </c>
       <c r="E80">
-        <v>-14.76539951494932</v>
+        <v>-15.41468758969509</v>
       </c>
       <c r="F80">
-        <v>0.5399877116154059</v>
+        <v>0.5906730278904994</v>
       </c>
       <c r="G80">
-        <v>-4.041797766676239</v>
+        <v>-5.71754386685713</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.66503516589525</v>
       </c>
       <c r="E81">
-        <v>-15.01846875639397</v>
+        <v>-15.90218234509481</v>
       </c>
       <c r="F81">
-        <v>0.4116073315295386</v>
+        <v>0.4566150176258441</v>
       </c>
       <c r="G81">
-        <v>-4.247884730381842</v>
+        <v>-4.211873323766937</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.48789888281609</v>
       </c>
       <c r="E82">
-        <v>-15.70737192175884</v>
+        <v>-17.09998183401965</v>
       </c>
       <c r="F82">
-        <v>0.535690969897085</v>
+        <v>0.8314711482102876</v>
       </c>
       <c r="G82">
-        <v>-3.31438047794138</v>
+        <v>-4.472310441383183</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.31787387386018</v>
       </c>
       <c r="E83">
-        <v>-17.00209433986985</v>
+        <v>-18.84376584862729</v>
       </c>
       <c r="F83">
-        <v>0.7888698694191146</v>
+        <v>0.8678712686241035</v>
       </c>
       <c r="G83">
-        <v>-3.344495529413964</v>
+        <v>-3.879219800848872</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.1535812178545</v>
       </c>
       <c r="E84">
-        <v>-17.31935017189922</v>
+        <v>-17.72887366183488</v>
       </c>
       <c r="F84">
-        <v>0.7326005284817498</v>
+        <v>1.388823244570685</v>
       </c>
       <c r="G84">
-        <v>-3.074017873825817</v>
+        <v>-3.596050380268793</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.995088990663906</v>
       </c>
       <c r="E85">
-        <v>-19.09921253892596</v>
+        <v>-20.6193623931388</v>
       </c>
       <c r="F85">
-        <v>0.654590685057912</v>
+        <v>0.827395580588514</v>
       </c>
       <c r="G85">
-        <v>-2.664485329769962</v>
+        <v>-1.938538028293735</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.841575561930789</v>
       </c>
       <c r="E86">
-        <v>-19.28839859754441</v>
+        <v>-20.90266372705866</v>
       </c>
       <c r="F86">
-        <v>0.6809054323426439</v>
+        <v>0.8807507250028302</v>
       </c>
       <c r="G86">
-        <v>-2.521492975430921</v>
+        <v>-1.33631574815949</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.690144740303074</v>
       </c>
       <c r="E87">
-        <v>-20.46543050467007</v>
+        <v>-21.2309418648227</v>
       </c>
       <c r="F87">
-        <v>0.5925053765854918</v>
+        <v>0.6484135493352361</v>
       </c>
       <c r="G87">
-        <v>-2.165769183728401</v>
+        <v>-1.76602452358437</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.543091519275958</v>
       </c>
       <c r="E88">
-        <v>-22.60723568523387</v>
+        <v>-24.29533305496918</v>
       </c>
       <c r="F88">
-        <v>0.400433483633176</v>
+        <v>1.053423910116387</v>
       </c>
       <c r="G88">
-        <v>-1.579926761618903</v>
+        <v>-1.264781836942036</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.401433599572442</v>
       </c>
       <c r="E89">
-        <v>-23.68293845796391</v>
+        <v>-22.34065347735034</v>
       </c>
       <c r="F89">
-        <v>0.7783148119726433</v>
+        <v>1.105471890769086</v>
       </c>
       <c r="G89">
-        <v>-1.233488826929611</v>
+        <v>0.009903833249488148</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.268872872174008</v>
       </c>
       <c r="E90">
-        <v>-25.0020331231842</v>
+        <v>-26.89548320374534</v>
       </c>
       <c r="F90">
-        <v>0.6606667599574464</v>
+        <v>0.9463590800393566</v>
       </c>
       <c r="G90">
-        <v>-1.024497982143899</v>
+        <v>-0.9986157064829991</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.146624863534338</v>
       </c>
       <c r="E91">
-        <v>-27.27798076080321</v>
+        <v>-28.70238508907188</v>
       </c>
       <c r="F91">
-        <v>0.5228529318884982</v>
+        <v>0.8393820569070228</v>
       </c>
       <c r="G91">
-        <v>-0.9952983914864005</v>
+        <v>-0.0553859133403428</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.033890795482598</v>
       </c>
       <c r="E92">
-        <v>-28.2968013715229</v>
+        <v>-29.78749803078985</v>
       </c>
       <c r="F92">
-        <v>0.5229150594437082</v>
+        <v>0.9576265334522355</v>
       </c>
       <c r="G92">
-        <v>-1.271459122815506</v>
+        <v>-0.6979704998773176</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.929701991228736</v>
       </c>
       <c r="E93">
-        <v>-30.10788077412152</v>
+        <v>-29.3326354590894</v>
       </c>
       <c r="F93">
-        <v>0.5980670353278877</v>
+        <v>1.071379601939469</v>
       </c>
       <c r="G93">
-        <v>-0.7542729806158295</v>
+        <v>-0.7049234083617809</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.832076733650577</v>
       </c>
       <c r="E94">
-        <v>-32.1426939635431</v>
+        <v>-32.65474436924941</v>
       </c>
       <c r="F94">
-        <v>0.4423339636015807</v>
+        <v>0.754633444661411</v>
       </c>
       <c r="G94">
-        <v>-0.5321309998198628</v>
+        <v>-1.02638140331902</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.741081036316283</v>
       </c>
       <c r="E95">
-        <v>-34.14751959808588</v>
+        <v>-33.57311663376795</v>
       </c>
       <c r="F95">
-        <v>0.1050467798363032</v>
+        <v>-0.1427411046283074</v>
       </c>
       <c r="G95">
-        <v>-0.8678229339019733</v>
+        <v>-1.26599588891903</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.651915856430859</v>
       </c>
       <c r="E96">
-        <v>-36.44182793356899</v>
+        <v>-35.98471923876074</v>
       </c>
       <c r="F96">
-        <v>0.08466065805340732</v>
+        <v>0.2335563852370073</v>
       </c>
       <c r="G96">
-        <v>-1.003540820043726</v>
+        <v>0.3322116645906237</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.56015408938018</v>
       </c>
       <c r="E97">
-        <v>-37.55673823425744</v>
+        <v>-38.7464657182636</v>
       </c>
       <c r="F97">
-        <v>0.2791265327998136</v>
+        <v>0.4179103790974401</v>
       </c>
       <c r="G97">
-        <v>-0.8369367953629202</v>
+        <v>0.3502715080538074</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.455590751333679</v>
       </c>
       <c r="E98">
-        <v>-39.96707739500209</v>
+        <v>-39.8924028586156</v>
       </c>
       <c r="F98">
-        <v>0.04970935222708778</v>
+        <v>0.5520694501852368</v>
       </c>
       <c r="G98">
-        <v>-1.670245666264178</v>
+        <v>0.3013845880396406</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.338662359273577</v>
       </c>
       <c r="E99">
-        <v>-41.68392151773809</v>
+        <v>-43.34082223003455</v>
       </c>
       <c r="F99">
-        <v>0.1215652542155281</v>
+        <v>-0.7554124045150581</v>
       </c>
       <c r="G99">
-        <v>-1.238984873041681</v>
+        <v>-0.4361454255414265</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.202873925855091</v>
       </c>
       <c r="E100">
-        <v>-44.86800933285531</v>
+        <v>-46.32497112500212</v>
       </c>
       <c r="F100">
-        <v>-0.2650619771626964</v>
+        <v>0.05313713653987213</v>
       </c>
       <c r="G100">
-        <v>-1.342684599206372</v>
+        <v>-1.014995564507747</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.053333977076814</v>
       </c>
       <c r="E101">
-        <v>-46.65337606003838</v>
+        <v>-47.63477789003268</v>
       </c>
       <c r="F101">
-        <v>-0.2049142200454243</v>
+        <v>-0.3362957752316342</v>
       </c>
       <c r="G101">
-        <v>-2.141940952763713</v>
+        <v>-2.505106554963054</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.880515353167028</v>
       </c>
       <c r="E102">
-        <v>-49.11702554891982</v>
+        <v>-50.24693528764017</v>
       </c>
       <c r="F102">
-        <v>-0.5149166382972916</v>
+        <v>-0.3647791883768953</v>
       </c>
       <c r="G102">
-        <v>-2.046162095443522</v>
+        <v>-0.8410776969709395</v>
       </c>
     </row>
   </sheetData>
